--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.96341240230132</v>
+        <v>10.23155451537396</v>
       </c>
       <c r="D2" t="n">
-        <v>64.02801984546778</v>
+        <v>10.40455322488851</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F2" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.00690661935271</v>
+        <v>8.288622325644816</v>
       </c>
       <c r="D3" t="n">
-        <v>52.19314679819503</v>
+        <v>8.481386354706693</v>
       </c>
       <c r="E3" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F3" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.84310063527614</v>
+        <v>10.69950385323237</v>
       </c>
       <c r="D4" t="n">
-        <v>66.77180110344108</v>
+        <v>10.85041767930918</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F4" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.60209933385479</v>
+        <v>10.1728411417514</v>
       </c>
       <c r="D5" t="n">
-        <v>63.59075112091224</v>
+        <v>10.33349705714824</v>
       </c>
       <c r="E5" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F5" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.00276681714855</v>
+        <v>6.82544960778664</v>
       </c>
       <c r="D6" t="n">
-        <v>43.17481839782387</v>
+        <v>7.015907989646379</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F6" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.03354924226447</v>
+        <v>6.992951751867976</v>
       </c>
       <c r="D7" t="n">
-        <v>44.13695214432878</v>
+        <v>7.172254723453428</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F7" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.86627962334445</v>
+        <v>7.453270438793474</v>
       </c>
       <c r="D8" t="n">
-        <v>46.84092499895566</v>
+        <v>7.611650312330294</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F8" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.01964385206954</v>
+        <v>4.065692125961299</v>
       </c>
       <c r="D9" t="n">
-        <v>26.02437386773365</v>
+        <v>4.228960753506718</v>
       </c>
       <c r="E9" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F9" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>45.67488643236492</v>
+        <v>7.4221690452593</v>
       </c>
       <c r="D10" t="n">
-        <v>46.36748409587569</v>
+        <v>7.5347161655798</v>
       </c>
       <c r="E10" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F10" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.11931449151698</v>
+        <v>3.594388604871509</v>
       </c>
       <c r="D11" t="n">
-        <v>23.22187840756206</v>
+        <v>3.773555241228835</v>
       </c>
       <c r="E11" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F11" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>51.48109551268895</v>
+        <v>8.365678020811956</v>
       </c>
       <c r="D12" t="n">
-        <v>52.04521318618613</v>
+        <v>8.457347142755246</v>
       </c>
       <c r="E12" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F12" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>47.62826426384292</v>
+        <v>7.739592942874474</v>
       </c>
       <c r="D13" t="n">
-        <v>47.92725335220099</v>
+        <v>7.788178669732661</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F13" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.54459478788663</v>
+        <v>4.150996653031577</v>
       </c>
       <c r="D14" t="n">
-        <v>25.46309968628944</v>
+        <v>4.137753699022033</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F14" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.05207330283269</v>
+        <v>4.558461911710311</v>
       </c>
       <c r="D15" t="n">
-        <v>27.07524233952048</v>
+        <v>4.399726880172078</v>
       </c>
       <c r="E15" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F15" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>49.99592735533076</v>
+        <v>8.124338195241249</v>
       </c>
       <c r="D16" t="n">
-        <v>49.57211158237871</v>
+        <v>8.055468132136541</v>
       </c>
       <c r="E16" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F16" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>24.06731937926615</v>
+        <v>3.910939399130749</v>
       </c>
       <c r="D17" t="n">
-        <v>22.939831952736</v>
+        <v>3.727722692319601</v>
       </c>
       <c r="E17" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F17" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.5147184006303</v>
+        <v>8.696141740102425</v>
       </c>
       <c r="D18" t="n">
-        <v>52.48184891795101</v>
+        <v>8.528300449167039</v>
       </c>
       <c r="E18" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F18" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>74.32923612403748</v>
+        <v>12.07850087015609</v>
       </c>
       <c r="D19" t="n">
-        <v>73.43733041299251</v>
+        <v>11.93356619211128</v>
       </c>
       <c r="E19" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F19" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>63.60855595926809</v>
+        <v>10.33639034338106</v>
       </c>
       <c r="D20" t="n">
-        <v>62.61984913865932</v>
+        <v>10.17572548503214</v>
       </c>
       <c r="E20" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F20" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>51.62972735698857</v>
+        <v>8.389830695510643</v>
       </c>
       <c r="D21" t="n">
-        <v>50.43934604137674</v>
+        <v>8.196393731723722</v>
       </c>
       <c r="E21" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F21" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>60.4302674100397</v>
+        <v>9.819918454131452</v>
       </c>
       <c r="D22" t="n">
-        <v>59.29423058734498</v>
+        <v>9.63531247044356</v>
       </c>
       <c r="E22" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F22" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>56.71477505345573</v>
+        <v>9.216150946186557</v>
       </c>
       <c r="D23" t="n">
-        <v>55.53241896430405</v>
+        <v>9.024018081699408</v>
       </c>
       <c r="E23" t="n">
-        <v>14.6702322077535</v>
+        <v>2.383912733759944</v>
       </c>
       <c r="F23" t="n">
-        <v>14.57385709876436</v>
+        <v>2.368251778549209</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
